--- a/tables_and_figures/table6_jaccard_subcategories.xlsx
+++ b/tables_and_figures/table6_jaccard_subcategories.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
